--- a/AAII_Financials/Quarterly/PCCWY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PCCWY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>PCCWY</t>
   </si>
@@ -656,131 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,47 +831,53 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>4607800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2337000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2634800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2147800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2533800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2417100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2518900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2215400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2562500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2385700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2704700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2303500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2382500</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -906,47 +920,53 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>2457200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1238600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1371900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1038200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1337300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1293300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1276300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1081600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1193400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1093900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1393400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1022600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1071200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,47 +1009,53 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>2150600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1098400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1263000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1109700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1196500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1123800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1242600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1133900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1369100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1291800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1311400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1280900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1311200</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,8 +1259,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1269,47 +1309,53 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>86200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-36100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>19100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-150000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>2500</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3400</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-251400</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1352,11 +1398,11 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1391,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,8 +1471,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1463,47 +1517,53 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>4128100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2124200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2214100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1837400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2074900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2109500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2059600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1938800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2145300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2079600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2299000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1940100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1838200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,47 +1606,53 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>479700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>212900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>420700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>310500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>458900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>307600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>459300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>276600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>417300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>306100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>405700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>363300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>544300</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,47 +1728,53 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>-212900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-130000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-128800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-116600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-116300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-117100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-89900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-113500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-100100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-78300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-107800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-95700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-102900</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1743,47 +1817,53 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>682500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>469600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>352700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>524600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>348300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>538500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>279100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>599800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>354300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>639600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>323400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>639500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>603800</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,11 +1906,11 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1856,17 +1936,23 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1909,47 +1995,53 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>266700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>82800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>291900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>193900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>342700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>190600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>369400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>163100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>317200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>227800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>298000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>267600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>441300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1992,47 +2084,53 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>90300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>50400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>66100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>53900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>88900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>55700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>109100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>27200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>42600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>8400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>30300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>26600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,8 +2212,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2158,47 +2262,53 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>176500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>32500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>225800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>140000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>253800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>134900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>260300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>135900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>274600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>219500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>267600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>241000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>387800</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2241,47 +2351,53 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>-68300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-74700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>66100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>20800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>90800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>23600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>104600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>10300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>152600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>111800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>156100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>136300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,36 +2529,36 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>-62400</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>8900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>138300</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2446,8 +2568,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,47 +2796,53 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>212900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>130000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>128800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>116600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>116300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>117100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>89900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>113500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>100100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>78300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>107800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>95700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2739,47 +2885,53 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>-130600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-74700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>66100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>20800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>90800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>23600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>113500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>148600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>152600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>111800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>156100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>136300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,8 +3013,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2905,135 +3063,147 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>-130600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-74700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>66100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>20800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>90800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>23600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>113500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>148600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>152600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>111800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>156100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>136300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,755 +3266,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>456100</v>
+      </c>
+      <c r="F41" s="3">
         <v>333000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>333100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>232600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>234700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>294600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>294500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>250500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>249900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>336300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>335500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>317000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>316400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>385900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>522600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>625000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>680400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>391500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>861400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1073400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1494000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1299900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>613000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>726100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>955800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>836600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1016700</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>61200</v>
+      </c>
+      <c r="F42" s="3">
         <v>219800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>219900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>64100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>64700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>93900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>93800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>23900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>23900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>64800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>64600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>10100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>10100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>65400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>68900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>64900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>62000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>49600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>77000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>125600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>219300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>409900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>58500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>44600</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>957300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>957500</v>
+      </c>
+      <c r="F43" s="3">
         <v>972100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>972400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>682000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>688200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>697500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>697300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>684400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>682900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>725300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>723600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>661000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>659900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>973200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>905800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>929100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>961400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>930000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>971000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>992800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>880500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>418600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>502200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>569600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>519200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>628200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>591200</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>234900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>234900</v>
+      </c>
+      <c r="F44" s="3">
         <v>219100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>219100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>272400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>274800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>273200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>273100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>286500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>285800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>205800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>205300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>253600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>253100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>264800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>174100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>187500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>337500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>319100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>261300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>152000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>116900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>138600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>121700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>149800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>98600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>128200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>102500</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F45" s="3">
         <v>422200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>422300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>104600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>105500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>369000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>368900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>328600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>327800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>307200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>545200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>540500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>619700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>632400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>566600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>582200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>656000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1271900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1351600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1192600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>991700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>932400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1027600</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2464100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2464800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2397500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2398400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2028300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2046500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1935100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1934600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1819900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1815800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1819200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1814800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1721100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1718100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2186100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2216700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2347100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2661100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2322600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2737400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2925900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3366600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3538900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2646900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2638800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2565500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2569800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2738000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>891200</v>
+      </c>
+      <c r="F47" s="3">
         <v>767300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>767500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>854300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>861900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>978400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>978200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>902200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>900200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>927900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>925700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>957700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>956100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1017500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>386600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>368700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>378700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>491100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>438900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>448300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>473000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>422200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>311000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>284400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>243200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>250300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4285500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4286600</v>
+      </c>
+      <c r="F48" s="3">
         <v>4211400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4212900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4025400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4061500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3980200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3979200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3900100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3891300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3822500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3813300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3727300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3720900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3702800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>5055300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4956700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4865100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4591900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4430700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>4291600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3831800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>3227400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>3076200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2964000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2757700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2632300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2574100</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5632400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5633900</v>
+      </c>
+      <c r="F49" s="3">
         <v>5385500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5387500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5406900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5455400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5047300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5046000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5088100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>5076600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4802700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4791100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4786700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4778500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4570900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4225000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>4119800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4039200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3761100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3720900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3563100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3559800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3815400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3880800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>3653800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3657200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>3667700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3490600</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>150700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>150800</v>
+      </c>
+      <c r="F52" s="3">
         <v>165900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>165900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>170400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>172000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>164900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>164900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>179900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>179500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>116000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>115700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>142200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>141900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>142100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>644700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>678800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>666900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>666900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>684200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>651100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>646000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>370000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>353800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>347500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>299700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>315400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>298100</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13853700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13857300</v>
+      </c>
+      <c r="F54" s="3">
         <v>13542700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13547600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12887900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13003400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12714300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12711100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12291600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12263800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12105100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12075700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>11717800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11697600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>12191900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12528300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>12471200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>12611100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>11833700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>12012100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>11880000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>11877300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>11373900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>10268700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>9888400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>9523400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>9435500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>9349000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1421800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1422200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1315600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1316100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1089900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1099700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>974600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>974300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>817900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>816000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>806100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>804100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>658600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>657500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>779000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>565700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>342900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>350200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>285600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>248800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>238900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>268000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>248300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>352400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>330200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>317700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>371100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1167100</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1237200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1237500</v>
+      </c>
+      <c r="F58" s="3">
         <v>894200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>894500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>291300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>294000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>663900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>663800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>650100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>648600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>305800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>294600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>284700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>284200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>664100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>496600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>582600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>370300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>441400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>282500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1214200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>265500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>68100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>59000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>300000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>494100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1409600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>617300</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>512700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>512900</v>
+      </c>
+      <c r="F59" s="3">
         <v>570400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>570600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>529000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>533800</v>
       </c>
       <c r="H59" s="3">
         <v>529000</v>
       </c>
       <c r="I59" s="3">
+        <v>533800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>529000</v>
+      </c>
+      <c r="K59" s="3">
         <v>528900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>478100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>477000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>489900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>499200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>535100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>534100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>529800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1285400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1324900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1356400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1274000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1328900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1464300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1408300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1514300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1405900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1466700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1416600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1365400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>649900</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4335300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4336500</v>
+      </c>
+      <c r="F60" s="3">
         <v>3874300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3875600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2900100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2926100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3256000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3255200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3012800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3006000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2658500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2652100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2331800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2327800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3126000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2347700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2250400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2076900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2001100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1860200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2917400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1941900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1830700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1817300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2096800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2228400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>3146000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2434300</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7505500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7507500</v>
+      </c>
+      <c r="F61" s="3">
         <v>7174700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7177300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7399900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7466300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6439300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6437700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6811200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6795900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6737800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6721500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6531200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6519900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5971900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7258000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7179500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7169400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6540000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>6651700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>5521000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6241100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5904600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>5823300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5306500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>4852300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>3968700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4671200</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>740700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>740900</v>
+      </c>
+      <c r="F62" s="3">
         <v>798900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>799200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>852900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>860500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>756500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>756300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>844900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>843000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>703400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>701700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>736000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>734800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>727800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1187000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1144400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1073000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1011400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1000500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>900600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1061400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>774600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>721700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>680400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>743100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>715800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>660200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13437700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13441200</v>
+      </c>
+      <c r="F66" s="3">
         <v>12668300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12672800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11945700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12052800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11231900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11229100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11437000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11411200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10863200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>10836900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>10342100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10324300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10554800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11256400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>10800200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10629700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>9829500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9832800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9642100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9413900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8884800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8717000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8409700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>8119100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>8119300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>8048900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2110700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-2111200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1810800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1811400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1726600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1742100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1406200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1405900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1567800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1564300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1276700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1273600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1142200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1140300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-931000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-398400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>102700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>404600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>426000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>642100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>667700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>859700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>892200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-67700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-139200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-87500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-168800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-173600</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>119100</v>
+      </c>
+      <c r="F76" s="3">
         <v>465600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>465800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>538300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>543200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>964000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>963800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>751900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>750200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1071100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1068500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1236400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1234300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1467200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1271900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1671000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1981400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2004100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2179300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2237900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2463400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2489100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1551700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1478600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1404300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1316200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1300100</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,96 +6387,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6141,47 +6531,53 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>-130600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-74700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>66100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>20800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>90800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>23600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>113500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>148600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>152600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>111800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>156100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>136300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,55 +6607,57 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>80800</v>
+      </c>
+      <c r="F83" s="3">
         <v>38800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>38700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>81100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>80900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>38400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>38300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>83500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>83300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>100100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>99400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>83300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>83500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -6294,8 +6692,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>341500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>341600</v>
+      </c>
+      <c r="F89" s="3">
         <v>458300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>458500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>323200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>326100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>400000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>399900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>282500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>281800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>531200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>530000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>322000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>321400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>460500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1625600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>713700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>871100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>548100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>549900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>284200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>870900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>653800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>840100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>443300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>950600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>644100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>844800</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-132800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-132900</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-139400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-139300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-140000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-139600</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-149500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1589000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1589000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-261800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-270400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-218200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-236100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-195400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-205000</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-252100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-252200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-268900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-271300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-246100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-246000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-247900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-247400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-311600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-310900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-165400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-165200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-164300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-965200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-383000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-702100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-456600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-483800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-254500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-118400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-667300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-733100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-563800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-591000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-707300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-115600</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,56 +7652,58 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>205000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>205100</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>205500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>205500</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>204200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>203700</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>199600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7269,8 +7737,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-156400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-156400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-84100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-84900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-132800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-132800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-76800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-76600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-211000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-210500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-189600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-189300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-241800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-828100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-385300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>123300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-559900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-271300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-442300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-94000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>696300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-217700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-119900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-241800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-107600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-868100</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3">
         <v>7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-2600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-7600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>3400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-8300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>4800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>1400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>62800</v>
+      </c>
+      <c r="F102" s="3">
         <v>49200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>49200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-29400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-29700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>21400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>21400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-43000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-42900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>9200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>9100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-33500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-33400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>52300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-160700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-57100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>288600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-469300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-212800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-409200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>197700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>687500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-113700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-240200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>119200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-175300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-143700</v>
       </c>
     </row>
